--- a/ExtraCredit/data_MPIvsOMP.xlsx
+++ b/ExtraCredit/data_MPIvsOMP.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crawfordd1\git\Labs\ExtraCredit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F96AA8CE-E304-40AD-A612-1F5359DDC2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB31774-0F91-409B-84F0-42F4B41BF244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16200" yWindow="-6270" windowWidth="16410" windowHeight="11295" xr2:uid="{B5D50531-28C4-4994-9788-CD83117EE451}"/>
+    <workbookView xWindow="-16320" yWindow="-6390" windowWidth="16440" windowHeight="28320" firstSheet="1" activeTab="1" xr2:uid="{B5D50531-28C4-4994-9788-CD83117EE451}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Increasing MPI Rank" sheetId="1" r:id="rId1"/>
+    <sheet name="Increasing Threadcount" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,6 +34,80 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="23">
+  <si>
+    <t>First Trial</t>
+  </si>
+  <si>
+    <t>Second Trial</t>
+  </si>
+  <si>
+    <t>Third Trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full work took </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of threads: </t>
+  </si>
+  <si>
+    <t>Number of ranks:</t>
+  </si>
+  <si>
+    <t>Number of threads:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 60060 x 40040</t>
+  </si>
+  <si>
+    <t>Image dimensions:</t>
+  </si>
+  <si>
+    <t>60060 x 40040</t>
+  </si>
+  <si>
+    <t>Area of Mandelbrot set :</t>
+  </si>
+  <si>
+    <t>Full work (seconds):</t>
+  </si>
+  <si>
+    <t>Average Times</t>
+  </si>
+  <si>
+    <t>Rank 2</t>
+  </si>
+  <si>
+    <t>Job Timeout</t>
+  </si>
+  <si>
+    <t>Rank 8</t>
+  </si>
+  <si>
+    <t>Area of Mandelbrot set:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of ranks: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image dimensions: </t>
+  </si>
+  <si>
+    <t>timeout</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Time on 2 Ranks</t>
+  </si>
+  <si>
+    <t>Time on 8 Ranks</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -83,6 +158,2688 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Increasing</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Rank vs Time</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Increasing MPI Rank'!$A$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>First Trial</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Increasing MPI Rank'!$B$22:$I$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Increasing MPI Rank'!$B$23:$I$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>63.962327999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75.691443000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53.605161000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.430045</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42.256686999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40.972307000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35.839100999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>34.344504000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0FDE-4026-9789-AC311F4C31F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Increasing MPI Rank'!$A$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Second Trial</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Increasing MPI Rank'!$B$22:$I$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Increasing MPI Rank'!$B$24:$I$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>64.280293999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53.698915999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.424473999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42.262731000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40.970734999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35.847709999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>34.343637999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0FDE-4026-9789-AC311F4C31F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Increasing MPI Rank'!$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Third Trial</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Increasing MPI Rank'!$B$22:$I$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Increasing MPI Rank'!$B$25:$I$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>64.295416000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53.633240999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.430594999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42.486832</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40.977035999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35.845874000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>34.334803999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0FDE-4026-9789-AC311F4C31F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Increasing MPI Rank'!$A$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average Times</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Increasing MPI Rank'!$B$22:$I$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Increasing MPI Rank'!$B$26:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>64.179345999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25.230481000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53.645772666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.428371333333331</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42.335416666666667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40.973359333333327</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35.844228333333341</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>34.340981999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0FDE-4026-9789-AC311F4C31F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="244891103"/>
+        <c:axId val="244887743"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="244891103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Rank</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Number</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="244887743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="244887743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Seconds</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="244891103"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Increasing Thread Count</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Increasing Threadcount'!$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Time on 2 Ranks</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Increasing Threadcount'!$B$15:$I$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Increasing Threadcount'!$B$16:$I$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="1">
+                  <c:v>53.213341999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40.961955000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.954595000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27.917403</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24.770527000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22.954685000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21.002725999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1F4F-45F6-AC1C-FEB0937EB10A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Increasing Threadcount'!$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Time on 8 Ranks</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Increasing Threadcount'!$B$15:$I$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Increasing Threadcount'!$B$17:$I$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>51.472206</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.324584999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.290037000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.394995000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.758044999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.466191999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15.296424999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14.113797</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1F4F-45F6-AC1C-FEB0937EB10A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="244937663"/>
+        <c:axId val="244938623"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="244937663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> of Threads</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="244938623"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="244938623"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> in Seconds</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="244937663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>295274</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFC82B34-FDA7-388F-FA82-C4D60635F102}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1423987</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>280987</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E72C1583-5859-DBBF-550C-E907DC7A2241}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +3159,1015 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300530D7-63D7-4140-9252-0A01E943F8E5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>1.521611</v>
+      </c>
+      <c r="C2">
+        <v>1.521611</v>
+      </c>
+      <c r="D2">
+        <v>1.521611</v>
+      </c>
+      <c r="E2">
+        <v>1.521611</v>
+      </c>
+      <c r="F2">
+        <v>1.521611</v>
+      </c>
+      <c r="G2">
+        <v>1.521611</v>
+      </c>
+      <c r="H2">
+        <v>1.521611</v>
+      </c>
+      <c r="I2">
+        <v>1.521611</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>63.962327999999999</v>
+      </c>
+      <c r="C4">
+        <v>75.691443000000007</v>
+      </c>
+      <c r="D4">
+        <v>53.605161000000003</v>
+      </c>
+      <c r="E4">
+        <v>52.430045</v>
+      </c>
+      <c r="F4">
+        <v>42.256686999999999</v>
+      </c>
+      <c r="G4">
+        <v>40.972307000000001</v>
+      </c>
+      <c r="H4">
+        <v>35.839100999999999</v>
+      </c>
+      <c r="I4">
+        <v>34.344504000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>16</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>16</v>
+      </c>
+      <c r="H5">
+        <v>16</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>1.521611</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>1.521611</v>
+      </c>
+      <c r="E8">
+        <v>1.521611</v>
+      </c>
+      <c r="F8">
+        <v>1.521611</v>
+      </c>
+      <c r="G8">
+        <v>1.521611</v>
+      </c>
+      <c r="H8">
+        <v>1.521611</v>
+      </c>
+      <c r="I8">
+        <v>1.521611</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>64.280293999999998</v>
+      </c>
+      <c r="D10">
+        <v>53.698915999999997</v>
+      </c>
+      <c r="E10">
+        <v>52.424473999999996</v>
+      </c>
+      <c r="F10">
+        <v>42.262731000000002</v>
+      </c>
+      <c r="G10">
+        <v>40.970734999999998</v>
+      </c>
+      <c r="H10">
+        <v>35.847709999999999</v>
+      </c>
+      <c r="I10">
+        <v>34.343637999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>16</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>16</v>
+      </c>
+      <c r="H11">
+        <v>16</v>
+      </c>
+      <c r="I11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>1.521611</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>1.521611</v>
+      </c>
+      <c r="E14">
+        <v>1.521611</v>
+      </c>
+      <c r="F14">
+        <v>1.521611</v>
+      </c>
+      <c r="G14">
+        <v>1.521611</v>
+      </c>
+      <c r="H14">
+        <v>1.521611</v>
+      </c>
+      <c r="I14">
+        <v>1.521611</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15">
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <v>8</v>
+      </c>
+      <c r="I15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>64.295416000000003</v>
+      </c>
+      <c r="D16">
+        <v>53.633240999999998</v>
+      </c>
+      <c r="E16">
+        <v>52.430594999999997</v>
+      </c>
+      <c r="F16">
+        <v>42.486832</v>
+      </c>
+      <c r="G16">
+        <v>40.977035999999998</v>
+      </c>
+      <c r="H16">
+        <v>35.845874000000002</v>
+      </c>
+      <c r="I16">
+        <v>34.334803999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>16</v>
+      </c>
+      <c r="D19">
+        <v>16</v>
+      </c>
+      <c r="E19">
+        <v>16</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>16</v>
+      </c>
+      <c r="H19">
+        <v>16</v>
+      </c>
+      <c r="I19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20">
+        <f>(B4+B10+B16)/3</f>
+        <v>64.179345999999995</v>
+      </c>
+      <c r="D20">
+        <f>(D4+D10+D16)/3</f>
+        <v>53.645772666666666</v>
+      </c>
+      <c r="E20">
+        <f>(E4+E10+E16)/3</f>
+        <v>52.428371333333331</v>
+      </c>
+      <c r="F20">
+        <f>(F4+F10+F16)/3</f>
+        <v>42.335416666666667</v>
+      </c>
+      <c r="G20">
+        <f>(G4+G10+G16)/3</f>
+        <v>40.973359333333327</v>
+      </c>
+      <c r="H20">
+        <f>(H4+H10+H16)/3</f>
+        <v>35.844228333333341</v>
+      </c>
+      <c r="I20">
+        <f>(I4+I10+I16)/3</f>
+        <v>34.340981999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22">
+        <v>7</v>
+      </c>
+      <c r="H22">
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23">
+        <v>63.962327999999999</v>
+      </c>
+      <c r="C23">
+        <v>75.691443000000007</v>
+      </c>
+      <c r="D23">
+        <v>53.605161000000003</v>
+      </c>
+      <c r="E23">
+        <v>52.430045</v>
+      </c>
+      <c r="F23">
+        <v>42.256686999999999</v>
+      </c>
+      <c r="G23">
+        <v>40.972307000000001</v>
+      </c>
+      <c r="H23">
+        <v>35.839100999999999</v>
+      </c>
+      <c r="I23">
+        <v>34.344504000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>64.280293999999998</v>
+      </c>
+      <c r="D24">
+        <v>53.698915999999997</v>
+      </c>
+      <c r="E24">
+        <v>52.424473999999996</v>
+      </c>
+      <c r="F24">
+        <v>42.262731000000002</v>
+      </c>
+      <c r="G24">
+        <v>40.970734999999998</v>
+      </c>
+      <c r="H24">
+        <v>35.847709999999999</v>
+      </c>
+      <c r="I24">
+        <v>34.343637999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>64.295416000000003</v>
+      </c>
+      <c r="D25">
+        <v>53.633240999999998</v>
+      </c>
+      <c r="E25">
+        <v>52.430594999999997</v>
+      </c>
+      <c r="F25">
+        <v>42.486832</v>
+      </c>
+      <c r="G25">
+        <v>40.977035999999998</v>
+      </c>
+      <c r="H25">
+        <v>35.845874000000002</v>
+      </c>
+      <c r="I25">
+        <v>34.334803999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26">
+        <f>(B23+B24+B25)/3</f>
+        <v>64.179345999999995</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ref="C26:J26" si="0">(C23+C24+C25)/3</f>
+        <v>25.230481000000001</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>53.645772666666666</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>52.428371333333331</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>42.335416666666667</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>40.973359333333327</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>35.844228333333341</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>34.340981999999997</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76C8C5B3-C7FB-4570-932F-46396F590FE1}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>1.521611</v>
+      </c>
+      <c r="D2">
+        <v>1.521611</v>
+      </c>
+      <c r="E2">
+        <v>1.521611</v>
+      </c>
+      <c r="F2">
+        <v>1.521611</v>
+      </c>
+      <c r="G2">
+        <v>1.521611</v>
+      </c>
+      <c r="H2">
+        <v>1.521611</v>
+      </c>
+      <c r="I2">
+        <v>1.521611</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>53.213341999999997</v>
+      </c>
+      <c r="D3">
+        <v>40.961955000000003</v>
+      </c>
+      <c r="E3">
+        <v>30.954595000000001</v>
+      </c>
+      <c r="F3">
+        <v>27.917403</v>
+      </c>
+      <c r="G3">
+        <v>24.770527000000001</v>
+      </c>
+      <c r="H3">
+        <v>22.954685000000001</v>
+      </c>
+      <c r="I3">
+        <v>21.002725999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>40</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>60</v>
+      </c>
+      <c r="H4">
+        <v>70</v>
+      </c>
+      <c r="I4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>1.521611</v>
+      </c>
+      <c r="C8">
+        <v>1.521611</v>
+      </c>
+      <c r="D8">
+        <v>1.521611</v>
+      </c>
+      <c r="E8">
+        <v>1.521611</v>
+      </c>
+      <c r="F8">
+        <v>1.521611</v>
+      </c>
+      <c r="G8">
+        <v>1.521611</v>
+      </c>
+      <c r="H8">
+        <v>1.521611</v>
+      </c>
+      <c r="I8">
+        <v>1.521611</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>51.472206</v>
+      </c>
+      <c r="C9">
+        <v>30.324584999999999</v>
+      </c>
+      <c r="D9">
+        <v>23.290037000000002</v>
+      </c>
+      <c r="E9">
+        <v>19.394995000000002</v>
+      </c>
+      <c r="F9">
+        <v>17.758044999999999</v>
+      </c>
+      <c r="G9">
+        <v>16.466191999999999</v>
+      </c>
+      <c r="H9">
+        <v>15.296424999999999</v>
+      </c>
+      <c r="I9">
+        <v>14.113797</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>40</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>60</v>
+      </c>
+      <c r="H10">
+        <v>70</v>
+      </c>
+      <c r="I10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+      <c r="E15">
+        <v>40</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15">
+        <v>60</v>
+      </c>
+      <c r="H15">
+        <v>70</v>
+      </c>
+      <c r="I15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>53.213341999999997</v>
+      </c>
+      <c r="D16">
+        <v>40.961955000000003</v>
+      </c>
+      <c r="E16">
+        <v>30.954595000000001</v>
+      </c>
+      <c r="F16">
+        <v>27.917403</v>
+      </c>
+      <c r="G16">
+        <v>24.770527000000001</v>
+      </c>
+      <c r="H16">
+        <v>22.954685000000001</v>
+      </c>
+      <c r="I16">
+        <v>21.002725999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <v>51.472206</v>
+      </c>
+      <c r="C17">
+        <v>30.324584999999999</v>
+      </c>
+      <c r="D17">
+        <v>23.290037000000002</v>
+      </c>
+      <c r="E17">
+        <v>19.394995000000002</v>
+      </c>
+      <c r="F17">
+        <v>17.758044999999999</v>
+      </c>
+      <c r="G17">
+        <v>16.466191999999999</v>
+      </c>
+      <c r="H17">
+        <v>15.296424999999999</v>
+      </c>
+      <c r="I17">
+        <v>14.113797</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>